--- a/Collections/EURO/Croatia/#EURO#Croatia#Commemorative#[2023-present]#UNC.xlsx
+++ b/Collections/EURO/Croatia/#EURO#Croatia#Commemorative#[2023-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Croatia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCE5344-DEAA-4B41-AEEC-91072793B6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D7B98C-1A39-42DE-817B-A00983CAC2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1430" windowWidth="33150" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>Year</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>400.000</t>
+  </si>
+  <si>
+    <t>Croatian Cities</t>
+  </si>
+  <si>
+    <t>Pula. Arena</t>
   </si>
 </sst>
 </file>
@@ -479,23 +485,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -558,9 +548,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -914,7 +904,9 @@
       <c r="B4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="20" t="s">
+        <v>32</v>
+      </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
       </c>
@@ -986,17 +978,23 @@
       <c r="A7" s="5">
         <v>2025</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="20"/>
+      <c r="B7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>32</v>
+      </c>
       <c r="D7" s="20" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="19"/>
+      <c r="F7" s="19" t="s">
+        <v>27</v>
+      </c>
       <c r="G7" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="str">
         <f>IF(OR(AND(G7&gt;1,G7&lt;&gt;"-")),"Can exchange","")</f>
@@ -1015,7 +1013,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G4">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1032,7 +1030,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1049,7 +1047,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1066,7 +1064,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
